--- a/stories/arbres/TREE-VIV-013.xlsx
+++ b/stories/arbres/TREE-VIV-013.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila marche à la ferme avec maman. Un animal fait un bruit. Maman dit : on nomme l'animal. On nomme le cri. Lila écoute. Elle va dire le nom et le cri.</t>
+          <t>Lila marche à la ferme avec maman. Un animal fait un bruit. On nomme l'animal. On nomme le cri. Lila écoute. Elle va dire le nom et le cri.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lila marche à la ferme avec maman. Un animal fait un bruit.
+maman|On nomme l'animal. On nomme le cri.
+narrateur|Lila écoute. Elle va dire le nom et le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cour, le pré, ou le poulailler.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la cour, un chien. Lila dit le nom : le chien. Le cri : ouah.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la cour, Lila entend. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a dit le nom de l'animal. Elle a dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chien, la vache, ou le coq.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien aboie. Lila dit le nom : le chien. Le cri : ouah.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend ouah à la cour. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend meuh à la cour. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3416,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend cocorico à la cour. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3583,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3750,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|La vache mugit. Lila dit le nom : la vache. Le cri : meuh.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3941,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4108,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend ouah à la cour. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4275,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4442,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend meuh à la cour. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4609,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4776,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend cocorico à la cour. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4943,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5110,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq chante. Lila dit le nom : le coq. Le cri : cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5301,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5468,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend ouah à la cour. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5635,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5802,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend meuh à la cour. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5969,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6136,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend cocorico à la cour. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6303,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6470,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le pré, une vache. Lila dit le nom : la vache. Le cri : meuh.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le pré, Lila entend. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Le nom. Le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6833,6 +7017,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chien, la vache, ou le coq.</t>
         </is>
       </c>
     </row>
@@ -6997,6 +7186,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le pré, le chien. Nom de l'animal. Cri : ouah.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7377,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7345,6 +7544,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend ouah à le pré. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7711,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7878,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend meuh à le pré. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8045,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8212,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend cocorico à le pré. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8379,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8546,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|La vache du pré. Nom. Cri : meuh.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8737,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8904,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend ouah à le pré. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9071,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9238,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend meuh à le pré. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9405,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9313,6 +9572,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend cocorico à le pré. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9739,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9906,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq au loin. Nom de l'animal. Cri : cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10097,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9985,6 +10264,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend ouah à le pré. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10431,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10598,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend meuh à le pré. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10765,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10932,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend cocorico à le pré. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11099,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11266,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Au poulailler, un coq. Lila dit le nom : le coq. Le cri : cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11447,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Au poulailler, Lila entend. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11620,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Lila nomme l'animal. Elle nomme le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11489,6 +11813,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chien, la vache, ou le coq.</t>
         </is>
       </c>
     </row>
@@ -11653,6 +11982,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Au poulailler, le chien passe. Nom. Cri : ouah.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11839,6 +12173,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12001,6 +12340,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend ouah à le poulailler. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12163,6 +12507,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12325,6 +12674,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend meuh à le poulailler. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12487,6 +12841,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12649,6 +13008,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend cocorico à le poulailler. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12811,6 +13175,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12973,6 +13342,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Une vache près du grillage. Nom de l'animal. Cri : meuh.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13159,6 +13533,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13321,6 +13700,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend ouah à le poulailler. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13483,6 +13867,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13645,6 +14034,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend meuh à le poulailler. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13807,6 +14201,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13969,6 +14368,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend cocorico à le poulailler. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14131,6 +14535,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14293,6 +14702,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq du poulailler. Nom. Cri : cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14479,6 +14893,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14641,6 +15060,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend ouah à le poulailler. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14803,6 +15227,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14965,6 +15394,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend meuh à le poulailler. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15127,6 +15561,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15289,6 +15728,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila entend cocorico à le poulailler. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15451,6 +15895,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15469,7 +15918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15493,6 +15942,13 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-VIV-013.xlsx
+++ b/stories/arbres/TREE-VIV-013.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Lila écoute. Elle va dire le nom et le cri.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre la cour, le pré, ou le poulailler.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,11 @@
           <t>narrateur|Dans la cour, un chien. Lila dit le nom : le chien. Le cri : ouah.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1878,7 @@
           <t>narrateur|Dans la cour, Lila entend. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2050,7 @@
           <t>narrateur|Lila a dit le nom de l'animal. Elle a dit le cri.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2240,11 @@
       <c r="AW7" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chien, la vache, ou le coq.</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2395,6 +2414,11 @@
           <t>narrateur|Le chien aboie. Lila dit le nom : le chien. Le cri : ouah.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2610,7 @@
           <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2753,6 +2778,11 @@
           <t>narrateur|Lila entend ouah à la cour. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2950,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3118,11 @@
           <t>narrateur|Lila entend meuh à la cour. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3421,6 +3458,11 @@
           <t>narrateur|Lila entend cocorico à la cour. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3588,6 +3630,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3755,6 +3798,7 @@
           <t>narrateur|La vache mugit. Lila dit le nom : la vache. Le cri : meuh.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3946,6 +3990,7 @@
           <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4113,6 +4158,7 @@
           <t>narrateur|Lila entend ouah à la cour. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4280,6 +4326,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4447,6 +4494,7 @@
           <t>narrateur|Lila entend meuh à la cour. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4614,6 +4662,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4781,6 +4830,7 @@
           <t>narrateur|Lila entend cocorico à la cour. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4948,6 +4998,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5115,6 +5166,7 @@
           <t>narrateur|Le coq chante. Lila dit le nom : le coq. Le cri : cocorico.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5306,6 +5358,7 @@
           <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5473,6 +5526,7 @@
           <t>narrateur|Lila entend ouah à la cour. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5640,6 +5694,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5807,6 +5862,7 @@
           <t>narrateur|Lila entend meuh à la cour. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5974,6 +6030,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6141,6 +6198,7 @@
           <t>narrateur|Lila entend cocorico à la cour. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6308,6 +6366,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6534,7 @@
           <t>narrateur|Dans le pré, une vache. Lila dit le nom : la vache. Le cri : meuh.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6718,7 @@
           <t>narrateur|Dans le pré, Lila entend. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6890,7 @@
           <t>narrateur|Oui. Le nom. Le cri.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7022,6 +7084,11 @@
       <c r="AW35" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chien, la vache, ou le coq.</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7191,6 +7258,11 @@
           <t>narrateur|Dans le pré, le chien. Nom de l'animal. Cri : ouah.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7382,6 +7454,7 @@
           <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7549,6 +7622,11 @@
           <t>narrateur|Lila entend ouah à le pré. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7716,6 +7794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7883,6 +7962,11 @@
           <t>narrateur|Lila entend meuh à le pré. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8050,6 +8134,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8217,6 +8302,11 @@
           <t>narrateur|Lila entend cocorico à le pré. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8384,6 +8474,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8551,6 +8642,7 @@
           <t>narrateur|La vache du pré. Nom. Cri : meuh.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8742,6 +8834,7 @@
           <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8909,6 +9002,7 @@
           <t>narrateur|Lila entend ouah à le pré. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9076,6 +9170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9243,6 +9338,7 @@
           <t>narrateur|Lila entend meuh à le pré. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9410,6 +9506,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9577,6 +9674,7 @@
           <t>narrateur|Lila entend cocorico à le pré. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9744,6 +9842,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9911,6 +10010,7 @@
           <t>narrateur|Le coq au loin. Nom de l'animal. Cri : cocorico.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10102,6 +10202,7 @@
           <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10269,6 +10370,7 @@
           <t>narrateur|Lila entend ouah à le pré. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10436,6 +10538,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10603,6 +10706,7 @@
           <t>narrateur|Lila entend meuh à le pré. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10770,6 +10874,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10937,6 +11042,7 @@
           <t>narrateur|Lila entend cocorico à le pré. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11104,6 +11210,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11271,6 +11378,7 @@
           <t>narrateur|Au poulailler, un coq. Lila dit le nom : le coq. Le cri : cocorico.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11454,6 +11562,7 @@
           <t>narrateur|Au poulailler, Lila entend. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11625,6 +11734,7 @@
           <t>narrateur|Lila nomme l'animal. Elle nomme le cri.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11818,6 +11928,11 @@
       <c r="AW63" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chien, la vache, ou le coq.</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -11987,6 +12102,11 @@
           <t>narrateur|Au poulailler, le chien passe. Nom. Cri : ouah.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12178,6 +12298,7 @@
           <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12345,6 +12466,11 @@
           <t>narrateur|Lila entend ouah à le poulailler. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12512,6 +12638,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12679,6 +12806,11 @@
           <t>narrateur|Lila entend meuh à le poulailler. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12846,6 +12978,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13013,6 +13146,11 @@
           <t>narrateur|Lila entend cocorico à le poulailler. Le nom de l'animal, c'est le chien. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13180,6 +13318,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13347,6 +13486,7 @@
           <t>narrateur|Une vache près du grillage. Nom de l'animal. Cri : meuh.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13538,6 +13678,7 @@
           <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13705,6 +13846,7 @@
           <t>narrateur|Lila entend ouah à le poulailler. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13872,6 +14014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14039,6 +14182,7 @@
           <t>narrateur|Lila entend meuh à le poulailler. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14206,6 +14350,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14373,6 +14518,7 @@
           <t>narrateur|Lila entend cocorico à le poulailler. Le nom de l'animal, c'est la vache. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14540,6 +14686,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14707,6 +14854,7 @@
           <t>narrateur|Le coq du poulailler. Nom. Cri : cocorico.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14898,6 +15046,7 @@
           <t>narrateur|On peut prendre ouah, meuh, ou cocorico.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15065,6 +15214,7 @@
           <t>narrateur|Lila entend ouah à le poulailler. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15232,6 +15382,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15399,6 +15550,7 @@
           <t>narrateur|Lila entend meuh à le poulailler. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15566,6 +15718,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15733,6 +15886,7 @@
           <t>narrateur|Lila entend cocorico à le poulailler. Le nom de l'animal, c'est le coq. Elle a dit le cri. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15900,6 +16054,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15918,7 +16073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15949,6 +16104,20 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15963,7 +16132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16150,6 +16319,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
